--- a/sample_data/SIGNAL_backlog_2026-09.xlsx
+++ b/sample_data/SIGNAL_backlog_2026-09.xlsx
@@ -471,52 +471,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COR-MAKM-KAVR</t>
+          <t>COR-UGR-KUD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COR-MAKM-KAVR-signal</t>
+          <t>COR-UGR-KUD-signal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4.22</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COR-RYP-BZA</t>
+          <t>COR-SZ-HWT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COR-RYP-BZA-signal</t>
+          <t>COR-SZ-HWT-signal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,37 +526,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5.08</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COR-SQF-HLX</t>
+          <t>COR-BP-PTF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COR-SQF-HLX-signal</t>
+          <t>COR-BP-PTF-signal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -566,24 +566,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-09-12 02:15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-09-12 05:10</t>
-        </is>
+        <v>3.29</v>
       </c>
     </row>
     <row r="5">
@@ -618,28 +605,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-12 02:15</t>
+          <t>2026-09-13 02:15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-12 04:32</t>
+          <t>2026-09-13 03:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COR-BZ-SFM</t>
+          <t>COR-LBA-MWP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COR-BZ-SFM-signal</t>
+          <t>COR-LBA-MWP-signal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,37 +636,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5.92</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COR-MTO-RMW</t>
+          <t>COR-NBS-NCB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COR-MTO-RMW-signal</t>
+          <t>COR-NBS-NCB-signal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -689,80 +676,67 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.88</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COR-TPH-BKLE</t>
+          <t>COR-CNC-RBG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COR-TPH-BKLE-signal</t>
+          <t>COR-CNC-RBG-signal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="H8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-09-12 08:45</t>
-        </is>
+        <v>2.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COR-BGN-KTP</t>
+          <t>COR-MJF-DYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COR-BGN-KTP-signal</t>
+          <t>COR-MJF-DYE-signal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -772,105 +746,115 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-09-19 05:15</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COR-MGS-VYN</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COR-MGS-VYN-signal</t>
+          <t>COR-KDH-TGH-signal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H10" t="n">
-        <v>30</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COR-VS-BRC</t>
+          <t>COR-UGR-KUD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COR-VS-BRC-signal</t>
+          <t>COR-UGR-KUD-signal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
+      </c>
+      <c r="H11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COR-RJY-GVN</t>
+          <t>COR-KHU-ATE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COR-RJY-GVN-signal</t>
+          <t>COR-KHU-ATE-signal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -880,32 +864,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6.3</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COR-SNAP-RPMN</t>
+          <t>COR-VINH-KFD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COR-SNAP-RPMN-signal</t>
+          <t>COR-VINH-KFD-signal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -915,87 +899,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:16</t>
-        </is>
+        <v>2.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COR-BRGW-DRGM</t>
+          <t>COR-USD-DSD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COR-BRGW-DRGM-signal</t>
+          <t>COR-USD-DSD-signal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3.96</v>
+        <v>4.69</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-14 02:00</t>
+          <t>2026-09-18 00:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-14 05:57</t>
+          <t>2026-09-18 04:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COR-BNDM-ROU</t>
+          <t>COR-BRLF-LMG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COR-BNDM-ROU-signal</t>
+          <t>COR-BRLF-LMG-signal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1005,61 +979,54 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-09-18 11:00</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-09-18 14:07</t>
-        </is>
+        <v>2.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COR-KNS-PHD</t>
+          <t>COR-NSS-KYY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COR-KNS-PHD-signal</t>
+          <t>COR-NSS-KYY-signal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1094,179 +1061,186 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COR-LTI-VJ</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COR-LTI-VJ-signal</t>
+          <t>COR-KHDI-PDH-signal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="H18" t="n">
-        <v>30</v>
+        <v>3.68</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-12 01:00</t>
+          <t>2026-09-19 01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-12 06:43</t>
+          <t>2026-09-19 04:40</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COR-JYM-SZK</t>
+          <t>COR-HLR-KPA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COR-JYM-SZK-signal</t>
+          <t>COR-HLR-KPA-signal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>30</v>
+        <v>3.39</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-09-17 01:23</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COR-KQN-ABI</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COR-KQN-ABI-signal</t>
+          <t>COR-GNJ-KNP-signal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4.87</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COR-AK-BSQ</t>
+          <t>COR-KDHA-VRG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COR-AK-BSQ-signal</t>
+          <t>COR-KDHA-VRG-signal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3.34</v>
+        <v>2.03</v>
+      </c>
+      <c r="H21" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COR-BANO-MCZ</t>
+          <t>COR-DXG-BHNE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COR-BANO-MCZ-signal</t>
+          <t>COR-DXG-BHNE-signal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1276,147 +1250,147 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3.79</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COR-KAYR-LNT</t>
+          <t>COR-SZ-HWT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COR-KAYR-LNT-signal</t>
+          <t>COR-SZ-HWT-signal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7.07</v>
+        <v>4.04</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-09-13 05:32</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COR-GNNA-BUP</t>
+          <t>COR-KKHT-DBG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COR-GNNA-BUP-signal</t>
+          <t>COR-KKHT-DBG-signal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-09-13 07:08</t>
-        </is>
+        <v>4.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COR-KKHT-DBG</t>
+          <t>COR-SNK-SNSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COR-KKHT-DBG-signal</t>
+          <t>COR-SNK-SNSL-signal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6.38</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COR-NGL-THJ</t>
+          <t>COR-HLR-KPA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COR-NGL-THJ-signal</t>
+          <t>COR-HLR-KPA-signal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1426,72 +1400,62 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-09-19 23:15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-09-20 03:01</t>
-        </is>
+        <v>4.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COR-ALP-PUC</t>
+          <t>COR-SHIV-ALN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COR-ALP-PUC-signal</t>
+          <t>COR-SHIV-ALN-signal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4.19</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COR-MTJL-GOPA</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COR-MTJL-GOPA-signal</t>
+          <t>COR-KKRD-VYA-signal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1506,87 +1470,87 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>6.75</v>
+        <v>2.56</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-14 11:00</t>
+          <t>2026-09-13 22:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45</t>
+          <t>2026-09-14 00:33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COR-KYJ-MVLK</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COR-KYJ-MVLK-signal</t>
+          <t>COR-KKRD-VYA-signal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6.73</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-14 22:15</t>
+          <t>2026-09-17 01:30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-15 04:58</t>
+          <t>2026-09-17 06:12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COR-GLE-BDCR</t>
+          <t>COR-CNC-RBG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COR-GLE-BDCR-signal</t>
+          <t>COR-CNC-RBG-signal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1596,37 +1560,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>4.15</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-20 10:00</t>
+          <t>2026-09-15 11:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-20 17:00</t>
+          <t>2026-09-15 15:09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COR-NRKP-TGB</t>
+          <t>COR-PRTP-MTC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COR-NRKP-TGB-signal</t>
+          <t>COR-PRTP-MTC-signal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1636,67 +1600,77 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2.92</v>
+        <v>4.84</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:50</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COR-AMPR-RMH</t>
+          <t>COR-LKA-DHRY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COR-AMPR-RMH-signal</t>
+          <t>COR-LKA-DHRY-signal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COR-KEB-BLD</t>
+          <t>COR-ANGR-BSRX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COR-KEB-BLD-signal</t>
+          <t>COR-ANGR-BSRX-signal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1706,47 +1680,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-09-15 14:30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:24</t>
-        </is>
+        <v>4.62</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COR-JSME-KBQ</t>
+          <t>COR-NRK-GDN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COR-JSME-KBQ-signal</t>
+          <t>COR-NRK-GDN-signal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1756,7 +1723,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1765,28 +1732,28 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.04</v>
+        <v>3.13</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-12 01:30</t>
+          <t>2026-09-18 01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-12 03:32</t>
+          <t>2026-09-18 04:07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COR-NDN-BEW</t>
+          <t>COR-CLA-LTT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COR-NDN-BEW-signal</t>
+          <t>COR-CLA-LTT-signal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1796,158 +1763,152 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="H35" t="n">
-        <v>20</v>
+        <v>4.63</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-09-13 06:07</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COR-ALJN-MWUE</t>
+          <t>COR-ANDI-NDAZ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COR-ALJN-MWUE-signal</t>
+          <t>COR-ANDI-NDAZ-signal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>7.37</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COR-DUM-RKR</t>
+          <t>COR-USD-DSD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COR-DUM-RKR-signal</t>
+          <t>COR-USD-DSD-signal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>15</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:15</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:51</t>
-        </is>
+        <v>3.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COR-BHLE-PJLE</t>
+          <t>COR-LKA-DHRY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COR-BHLE-PJLE-signal</t>
+          <t>COR-LKA-DHRY-signal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3.93</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COR-BGP-AKN</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COR-BGP-AKN-signal</t>
+          <t>COR-KKRD-VYA-signal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1957,37 +1918,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-09-18 14:00</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-09-18 19:32</t>
-        </is>
+        <v>3.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COR-VJ-KVN</t>
+          <t>COR-IDJ-KNP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COR-VJ-KVN-signal</t>
+          <t>COR-IDJ-KNP-signal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1997,55 +1948,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H40" t="n">
-        <v>15</v>
+        <v>2.6</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-12 01:00</t>
+          <t>2026-09-13 02:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-12 03:27</t>
+          <t>2026-09-13 04:36</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COR-PANP-S</t>
+          <t>COR-NZB-JKM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COR-PANP-S-signal</t>
+          <t>COR-NZB-JKM-signal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2055,37 +2003,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-09-12 02:00</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-09-12 05:52</t>
-        </is>
+        <v>1.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COR-NZB-JKM</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COR-NZB-JKM-signal</t>
+          <t>COR-KHTG-KBH-signal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2100,57 +2038,67 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2.38</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COR-RTGN-SAO</t>
+          <t>COR-SZ-HWT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COR-RTGN-SAO-signal</t>
+          <t>COR-SZ-HWT-signal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:15</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:51</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COR-PRSR-SURP</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COR-PRSR-SURP-signal</t>
+          <t>COR-KBH-KHTG-signal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2160,37 +2108,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>4.63</v>
+        <v>1.94</v>
+      </c>
+      <c r="H44" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COR-CTHR-KTHA</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COR-CTHR-KTHA-signal</t>
+          <t>COR-GNJ-KNP-signal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2200,30 +2151,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>7.07</v>
+        <v>3.4</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COR-CAM-PKA</t>
+          <t>COR-PRTP-MTC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COR-CAM-PKA-signal</t>
+          <t>COR-PRTP-MTC-signal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2233,75 +2184,82 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>7.64</v>
+        <v>3.26</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:30</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COR-NIM-BRMD</t>
+          <t>COR-GAG-KITA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COR-NIM-BRMD-signal</t>
+          <t>COR-GAG-KITA-signal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="H47" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COR-BWX-BTI</t>
+          <t>COR-KDHA-VRG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COR-BWX-BTI-signal</t>
+          <t>COR-KDHA-VRG-signal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2311,177 +2269,167 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>4.14</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COR-PLJ-LKD</t>
+          <t>COR-DXG-BHNE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COR-PLJ-LKD-signal</t>
+          <t>COR-DXG-BHNE-signal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3.33</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COR-GZM-MLDT</t>
+          <t>COR-LS-SUM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COR-GZM-MLDT-signal</t>
+          <t>COR-LS-SUM-signal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-09-12 14:30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-09-12 22:18</t>
-        </is>
+        <v>2.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COR-CTHT-NWD</t>
+          <t>COR-KKA-HWR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COR-CTHT-NWD-signal</t>
+          <t>COR-KKA-HWR-signal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>7.02</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>COR-LS-SUM</t>
+          <t>COR-TKC-PNB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COR-LS-SUM-signal</t>
+          <t>COR-TKC-PNB-signal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COR-KKA-HWR</t>
+          <t>COR-SHIV-ALN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COR-KKA-HWR-signal</t>
+          <t>COR-SHIV-ALN-signal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2491,122 +2439,112 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>7.52</v>
+        <v>4.86</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-09-16 02:51</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COR-SHK-KSC</t>
+          <t>COR-MER-SNKB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COR-SHK-KSC-signal</t>
+          <t>COR-MER-SNKB-signal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-09-20 02:00</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-09-20 08:21</t>
-        </is>
+        <v>4.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COR-PGI-TA</t>
+          <t>COR-BPK-SEGM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COR-PGI-TA-signal</t>
+          <t>COR-BPK-SEGM-signal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-09-14 22:00</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-09-15 05:45</t>
-        </is>
+        <v>1.97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COR-MER-SNKB</t>
+          <t>COR-LBA-MWP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>COR-MER-SNKB-signal</t>
+          <t>COR-LBA-MWP-signal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2616,32 +2554,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>7.97</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COR-RDDE-HNN</t>
+          <t>COR-LBA-MWP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COR-RDDE-HNN-signal</t>
+          <t>COR-LBA-MWP-signal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2651,162 +2589,168 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
+      </c>
+      <c r="H57" t="n">
+        <v>20</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:30</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:13</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COR-KTPK-BKWA</t>
+          <t>COR-MANW-SD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COR-KTPK-BKWA-signal</t>
+          <t>COR-MANW-SD-signal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-09-19 01:00</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-09-19 05:09</t>
-        </is>
+        <v>1.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COR-VN-KDY</t>
+          <t>COR-IGTA-BSZ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COR-VN-KDY-signal</t>
+          <t>COR-IGTA-BSZ-signal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COR-SCC-BVN</t>
+          <t>COR-MTN-DR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COR-SCC-BVN-signal</t>
+          <t>COR-MTN-DR-signal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
+      </c>
+      <c r="H60" t="n">
+        <v>30</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00</t>
+          <t>2026-09-18 22:15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-09-14 12:54</t>
+          <t>2026-09-19 01:04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COR-KORI-KUND</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COR-KORI-KUND-signal</t>
+          <t>COR-KDH-TGH-signal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2816,160 +2760,173 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2.96</v>
+        <v>3.94</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-20 11:15</t>
+          <t>2026-09-13 00:15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-09-20 14:12</t>
+          <t>2026-09-13 04:11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COR-KTKR-HER</t>
+          <t>COR-RJQ-LKMN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COR-KTKR-HER-signal</t>
+          <t>COR-RJQ-LKMN-signal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COR-SONW-WRS</t>
+          <t>COR-DXG-BHNE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COR-SONW-WRS-signal</t>
+          <t>COR-DXG-BHNE-signal</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="H63" t="n">
-        <v>20</v>
+        <v>1.96</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-12 11:30</t>
+          <t>2026-09-22 11:15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-09-12 19:26</t>
+          <t>2026-09-22 13:12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COR-TMPY-KAVR</t>
+          <t>COR-CUE-TISI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COR-TMPY-KAVR-signal</t>
+          <t>COR-CUE-TISI-signal</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>4.85</v>
+        <v>1.84</v>
+      </c>
+      <c r="H64" t="n">
+        <v>20</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:30</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:20</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COR-MWY-DRR</t>
+          <t>COR-MMA-SAA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>COR-MWY-DRR-signal</t>
+          <t>COR-MMA-SAA-signal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2979,37 +2936,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>6.85</v>
+        <v>4.88</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-09-20 22:00</t>
+          <t>2026-09-18 11:15</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-09-21 04:51</t>
+          <t>2026-09-18 16:07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COR-KWB-BHV</t>
+          <t>COR-KDH-TGH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>COR-KWB-BHV-signal</t>
+          <t>COR-KDH-TGH-signal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3024,32 +2981,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>6.31</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COR-CLDR-SGDP</t>
+          <t>COR-PRDG-ACLE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COR-CLDR-SGDP-signal</t>
+          <t>COR-PRDG-ACLE-signal</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3059,67 +3016,80 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>7.2</v>
+        <v>1.59</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:50</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COR-KDPR-BAHN</t>
+          <t>COR-DXG-BHNE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COR-KDPR-BAHN-signal</t>
+          <t>COR-DXG-BHNE-signal</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>6.85</v>
+        <v>3.09</v>
+      </c>
+      <c r="H68" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COR-KSP-RBZ</t>
+          <t>COR-KHDI-PDH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COR-KSP-RBZ-signal</t>
+          <t>COR-KHDI-PDH-signal</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3129,70 +3099,87 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>7.05</v>
+        <v>3.06</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:15</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:18</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COR-JOP-ZBD</t>
+          <t>COR-DDGA-PLJE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COR-JOP-ZBD-signal</t>
+          <t>COR-DDGA-PLJE-signal</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="H70" t="n">
-        <v>20</v>
+        <v>2.85</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:30</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:21</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>COR-PRDG-ACLE</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COR-PRDG-ACLE-signal</t>
+          <t>COR-KBH-KHTG-signal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3202,27 +3189,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COR-BUDI-SNAR</t>
+          <t>COR-SBI-SBT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COR-BUDI-SNAR-signal</t>
+          <t>COR-SBI-SBT-signal</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3232,32 +3219,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3.06</v>
+        <v>3.89</v>
+      </c>
+      <c r="H72" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COR-DGB-KBM</t>
+          <t>COR-LKA-DHRY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>COR-DGB-KBM-signal</t>
+          <t>COR-LKA-DHRY-signal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3267,150 +3257,147 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>2.04</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COR-PLY-SRJN</t>
+          <t>COR-GAG-KITA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COR-PLY-SRJN-signal</t>
+          <t>COR-GAG-KITA-signal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3.53</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COR-ATM-DQG</t>
+          <t>COR-SNK-SNSL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COR-ATM-DQG-signal</t>
+          <t>COR-SNK-SNSL-signal</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="H75" t="n">
-        <v>30</v>
+        <v>1.62</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-09-14 01:52</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COR-RJK-HZN</t>
+          <t>COR-CKDL-HRNR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>COR-RJK-HZN-signal</t>
+          <t>COR-CKDL-HRNR-signal</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:00</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>2026-09-18 02:57</t>
-        </is>
+        <v>4.09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COR-GAW-KPE</t>
+          <t>COR-BRGT-KEQ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COR-GAW-KPE-signal</t>
+          <t>COR-BRGT-KEQ-signal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3425,183 +3412,203 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-09-19 02:00</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>2026-09-19 06:15</t>
-        </is>
+        <v>3.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COR-NXN-BANO</t>
+          <t>COR-RPK-GGD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COR-NXN-BANO-signal</t>
+          <t>COR-RPK-GGD-signal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H78" t="n">
-        <v>20</v>
+        <v>2.37</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-09-17 22:15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:37</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COR-SRB-DRTP</t>
+          <t>COR-TVNL-KDMD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>COR-SRB-DRTP-signal</t>
+          <t>COR-TVNL-KDMD-signal</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>5.09</v>
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COR-MTA-SGBJ</t>
+          <t>COR-BSR-JCNR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>COR-MTA-SGBJ-signal</t>
+          <t>COR-BSR-JCNR-signal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H80" t="n">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:15</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:15</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COR-CKDL-HRNR</t>
+          <t>COR-SBI-SBT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COR-CKDL-HRNR-signal</t>
+          <t>COR-SBI-SBT-signal</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>6.43</v>
+        <v>1.67</v>
+      </c>
+      <c r="H81" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:30</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:10</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>COR-HNH-KAG</t>
+          <t>COR-SPGL-PFM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COR-HNH-KAG-signal</t>
+          <t>COR-SPGL-PFM-signal</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3611,35 +3618,32 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="H82" t="n">
-        <v>30</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>COR-GNS-VNK</t>
+          <t>COR-RC-YS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COR-GNS-VNK-signal</t>
+          <t>COR-RC-YS-signal</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3649,75 +3653,82 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H83" t="n">
-        <v>30</v>
+        <v>3.12</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:07</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COR-RWJ-AMLI</t>
+          <t>COR-KKRD-VYA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COR-RWJ-AMLI-signal</t>
+          <t>COR-KKRD-VYA-signal</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>4.49</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>COR-KHRI-GMO</t>
+          <t>COR-PLV-WTR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>COR-KHRI-GMO-signal</t>
+          <t>COR-PLV-WTR-signal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3727,27 +3738,27 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>COR-GNW-CWA</t>
+          <t>COR-LKU-HDW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>COR-GNW-CWA-signal</t>
+          <t>COR-LKU-HDW-signal</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3762,90 +3773,67 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-09-14 10:15</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2026-09-14 14:49</t>
-        </is>
+        <v>3.18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>COR-RAU-HKH</t>
+          <t>COR-HDT-RTB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COR-RAU-HKH-signal</t>
+          <t>COR-HDT-RTB-signal</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="H87" t="n">
-        <v>20</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-09-12 14:30</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>2026-09-12 21:04</t>
-        </is>
+        <v>2.41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>COR-NNU-RE</t>
+          <t>COR-TVNL-KDMD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>COR-NNU-RE-signal</t>
+          <t>COR-TVNL-KDMD-signal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3855,42 +3843,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-09-16 11:15</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2026-09-16 13:58</t>
-        </is>
+        <v>3.29</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>COR-RGP-GNP</t>
+          <t>COR-CRV-KLD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>COR-RGP-GNP-signal</t>
+          <t>COR-CRV-KLD-signal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3900,27 +3878,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>7.83</v>
+        <v>1.85</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:30</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:21</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>COR-TLMD-JLL</t>
+          <t>COR-LKA-DHRY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>COR-TLMD-JLL-signal</t>
+          <t>COR-LKA-DHRY-signal</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3935,32 +3923,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3.99</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>COR-LMNR-INDM</t>
+          <t>COR-JHT-SCKR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>COR-LMNR-INDM-signal</t>
+          <t>COR-JHT-SCKR-signal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3970,47 +3958,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-09-16 01:30</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2026-09-16 06:30</t>
-        </is>
+        <v>4.24</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>COR-SJV-GNK</t>
+          <t>COR-KDHA-VRG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>COR-SJV-GNK-signal</t>
+          <t>COR-KDHA-VRG-signal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4020,62 +3998,75 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>6.89</v>
+        <v>2.78</v>
+      </c>
+      <c r="H92" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>COR-HDM-GNL</t>
+          <t>COR-LIN-SRPM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COR-HDM-GNL-signal</t>
+          <t>COR-LIN-SRPM-signal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>interlocking_fault</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>5.64</v>
+        <v>4.43</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:30</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:55</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>COR-KKU-DNK</t>
+          <t>COR-PLV-WTR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COR-KKU-DNK-signal</t>
+          <t>COR-PLV-WTR-signal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>interlocking_fault</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4094,53 +4085,63 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>7.48</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>COR-GHS-JWN</t>
+          <t>COR-SBI-SBT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COR-GHS-JWN-signal</t>
+          <t>COR-SBI-SBT-signal</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>track_circuit_failure</t>
+          <t>signal_relay_fault</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>5.06</v>
+        <v>1.79</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:00</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-09-14 23:47</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>COR-CRV-KLD</t>
+          <t>COR-KHTG-KBH</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COR-CRV-KLD-signal</t>
+          <t>COR-KHTG-KBH-signal</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4150,42 +4151,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-09-19 10:30</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>2026-09-19 13:06</t>
-        </is>
+        <v>2.56</v>
+      </c>
+      <c r="H96" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>COR-KAH-BET</t>
+          <t>COR-JU-BGKT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COR-KAH-BET-signal</t>
+          <t>COR-JU-BGKT-signal</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4195,35 +4189,32 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="H97" t="n">
-        <v>15</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>COR-JHT-SCKR</t>
+          <t>COR-KBH-KHTG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>COR-JHT-SCKR-signal</t>
+          <t>COR-KBH-KHTG-signal</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4238,32 +4229,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>6.69</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COR-TRA-BTR</t>
+          <t>COR-GNJ-KNP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>COR-TRA-BTR-signal</t>
+          <t>COR-GNJ-KNP-signal</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>cable_fault</t>
+          <t>track_circuit_failure</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4273,32 +4264,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2.58</v>
+        <v>1.84</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:00</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:50</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>COR-TLO-KHN</t>
+          <t>COR-SHIV-ALN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>COR-TLO-KHN-signal</t>
+          <t>COR-SHIV-ALN-signal</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4308,60 +4309,60 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3.23</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>COR-UMNR-KGG</t>
+          <t>COR-DMA-BURN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COR-UMNR-KGG-signal</t>
+          <t>COR-DMA-BURN-signal</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>signal_relay_fault</t>
+          <t>cable_fault</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-09-16 00:15</t>
+          <t>2026-09-15 00:15</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-09-16 04:48</t>
+          <t>2026-09-15 04:34</t>
         </is>
       </c>
     </row>
